--- a/clients/Poojamani/AY 2026-27/Tax Audit Applicability/tax_audit_applicability_result.xlsx
+++ b/clients/Poojamani/AY 2026-27/Tax Audit Applicability/tax_audit_applicability_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Client Name</t>
   </si>
@@ -28,6 +28,24 @@
     <t>Activity Type</t>
   </si>
   <si>
+    <t>Presumptive Section</t>
+  </si>
+  <si>
+    <t>Presumptive Section Display</t>
+  </si>
+  <si>
+    <t>Business Nature</t>
+  </si>
+  <si>
+    <t>Is Resident</t>
+  </si>
+  <si>
+    <t>Section 44AD(4) Applicable</t>
+  </si>
+  <si>
+    <t>Section 44AD(4) Display</t>
+  </si>
+  <si>
     <t>Turnover / Gross Receipts</t>
   </si>
   <si>
@@ -52,24 +70,42 @@
     <t>Cash Payments %</t>
   </si>
   <si>
-    <t>Profit Amount</t>
-  </si>
-  <si>
-    <t>Profit Amount Formatted</t>
-  </si>
-  <si>
-    <t>Profit %</t>
+    <t>Digital / Banking Turnover</t>
+  </si>
+  <si>
+    <t>Digital / Banking Turnover Formatted</t>
+  </si>
+  <si>
+    <t>Declared Profit Amount</t>
+  </si>
+  <si>
+    <t>Declared Profit Amount Formatted</t>
+  </si>
+  <si>
+    <t>Declared Profit %</t>
+  </si>
+  <si>
+    <t>44AD Presumptive Profit</t>
+  </si>
+  <si>
+    <t>44AD Presumptive Profit Formatted</t>
+  </si>
+  <si>
+    <t>44ADA Presumptive Profit</t>
+  </si>
+  <si>
+    <t>44ADA Presumptive Profit Formatted</t>
+  </si>
+  <si>
+    <t>Presumptive Profit 44AE</t>
+  </si>
+  <si>
+    <t>Presumptive Profit 44AE Formatted</t>
   </si>
   <si>
     <t>Total Income Above Basic Exemption</t>
   </si>
   <si>
-    <t>Opted Presumptive Last Year</t>
-  </si>
-  <si>
-    <t>Wants To Opt Presumptive</t>
-  </si>
-  <si>
     <t>Accounts Audited Under Other Law</t>
   </si>
   <si>
@@ -103,13 +139,13 @@
     <t>Business</t>
   </si>
   <si>
-    <t>99,00,000</t>
-  </si>
-  <si>
-    <t>3,50,000</t>
-  </si>
-  <si>
-    <t>12,00,000</t>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>Not Applicable - Normal Business / Profession</t>
+  </si>
+  <si>
+    <t>Eligible Business</t>
   </si>
   <si>
     <t>Yes</t>
@@ -118,19 +154,43 @@
     <t>No</t>
   </si>
   <si>
+    <t>No - Section 44AD(4) not applicable</t>
+  </si>
+  <si>
+    <t>12,00,00,000</t>
+  </si>
+  <si>
+    <t>5,00,000</t>
+  </si>
+  <si>
+    <t>4,00,000</t>
+  </si>
+  <si>
+    <t>11,95,00,000</t>
+  </si>
+  <si>
+    <t>1,20,00,000</t>
+  </si>
+  <si>
+    <t>72,10,000</t>
+  </si>
+  <si>
+    <t>6,00,00,000</t>
+  </si>
+  <si>
     <t>Normal Basis</t>
   </si>
   <si>
-    <t>Form 3CB-3CD</t>
+    <t>Form 3CA-3CD</t>
   </si>
   <si>
     <t>ITR-3 for normal business/professional income</t>
   </si>
   <si>
-    <t>Section 44AB(e) read with Section 44AD</t>
-  </si>
-  <si>
-    <t>Accounts are not required to be audited under another law. Therefore, Form 3CB-3CD will apply if tax audit is applicable. | Business turnover is within applicable audit limit of ₹10,00,00,000. | Client does not want to opt presumptive taxation. | Client opted out of presumptive taxation after earlier opting in and income exceeds basic exemption limit.</t>
+    <t>Section 44AB(a)</t>
+  </si>
+  <si>
+    <t>Accounts are required to be audited under another law. If tax audit applies, Form 3CA-3CD will be applicable. | Business turnover exceeds applicable audit limit of ₹10,00,00,000. | Since tax audit is applicable, applicable audit report is Form 3CA-3CD.</t>
   </si>
 </sst>
 </file>
@@ -462,10 +522,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -541,82 +601,151 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2">
-        <v>9900000</v>
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2">
-        <v>350000</v>
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2">
-        <v>3.54</v>
-      </c>
-      <c r="J2">
-        <v>350000</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2">
-        <v>3.54</v>
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2">
+        <v>120000000</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
       </c>
       <c r="M2">
-        <v>1200000</v>
+        <v>500000</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="O2">
-        <v>12.12</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
+        <v>0.42</v>
+      </c>
+      <c r="P2">
+        <v>400000</v>
       </c>
       <c r="Q2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
+        <v>49</v>
+      </c>
+      <c r="R2">
+        <v>0.33</v>
+      </c>
+      <c r="S2">
+        <v>119500000</v>
       </c>
       <c r="T2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
+        <v>50</v>
+      </c>
+      <c r="U2">
+        <v>12000000</v>
       </c>
       <c r="V2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X2" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="W2">
+        <v>10</v>
+      </c>
+      <c r="X2">
+        <v>7210000</v>
       </c>
       <c r="Y2" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="Z2">
+        <v>60000000</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
